--- a/data/trans_orig/P6702-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6702-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2012</t>
+          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43512</t>
+          <t>43337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69556</t>
+          <t>69499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>42191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68788</t>
+          <t>70633</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105566</t>
+          <t>104390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64413</t>
+          <t>64391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28153</t>
+          <t>28675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50946</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71580</t>
+          <t>69250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104877</t>
+          <t>106043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>71349</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103063</t>
+          <t>102732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65647</t>
+          <t>64958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>122405</t>
+          <t>121945</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161066</t>
+          <t>161947</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45822</t>
+          <t>46074</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72499</t>
+          <t>73000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34030</t>
+          <t>35372</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67120</t>
+          <t>67034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100593</t>
+          <t>101032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28987</t>
+          <t>29163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44794</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59866</t>
+          <t>60329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94171</t>
+          <t>94033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46024</t>
+          <t>45057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74134</t>
+          <t>73660</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115358</t>
+          <t>112274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159792</t>
+          <t>156605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39631</t>
+          <t>39856</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69655</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56012</t>
+          <t>55660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115538</t>
+          <t>114649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114283</t>
+          <t>117225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>155361</t>
+          <t>154869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74257</t>
+          <t>74708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>107260</t>
+          <t>109350</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>199549</t>
+          <t>201352</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>251411</t>
+          <t>253244</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72425</t>
+          <t>73966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106083</t>
+          <t>107849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>37414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64305</t>
+          <t>64318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119690</t>
+          <t>117888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162152</t>
+          <t>162264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42600</t>
+          <t>41508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73589</t>
+          <t>71948</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>19436</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40447</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69025</t>
+          <t>69348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105251</t>
+          <t>105905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>30605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56512</t>
+          <t>54880</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34465</t>
+          <t>35178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58575</t>
+          <t>60909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71129</t>
+          <t>71210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106239</t>
+          <t>108013</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64073</t>
+          <t>63690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39769</t>
+          <t>38978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59590</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94052</t>
+          <t>93670</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85570</t>
+          <t>84723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120106</t>
+          <t>120120</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47449</t>
+          <t>47265</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74066</t>
+          <t>75671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>140736</t>
+          <t>139511</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>186785</t>
+          <t>182476</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52288</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>81757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52309</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>86054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>125593</t>
+          <t>123568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51130</t>
+          <t>50618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82351</t>
+          <t>82880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29130</t>
+          <t>28088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53062</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>86771</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125358</t>
+          <t>125954</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>58314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94757</t>
+          <t>93831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88842</t>
+          <t>89605</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129569</t>
+          <t>129064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175155</t>
+          <t>174581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47984</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78560</t>
+          <t>77966</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31700</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56409</t>
+          <t>55595</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>86922</t>
+          <t>87415</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127089</t>
+          <t>126279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>142543</t>
+          <t>141112</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>181693</t>
+          <t>180900</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>88382</t>
+          <t>89872</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121072</t>
+          <t>124129</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>240667</t>
+          <t>240241</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>292384</t>
+          <t>294490</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64362</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95831</t>
+          <t>95715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45267</t>
+          <t>45108</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>74916</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116857</t>
+          <t>117497</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159634</t>
+          <t>161970</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27258</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>51555</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29681</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44369</t>
+          <t>44528</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73394</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>217617</t>
+          <t>215803</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>279076</t>
+          <t>277016</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>183641</t>
+          <t>181933</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>236174</t>
+          <t>239420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>419012</t>
+          <t>418870</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>500890</t>
+          <t>501195</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>188390</t>
+          <t>185001</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>244320</t>
+          <t>242752</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129376</t>
+          <t>127400</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175207</t>
+          <t>175424</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>325878</t>
+          <t>326799</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>402818</t>
+          <t>400888</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>451667</t>
+          <t>453313</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>524055</t>
+          <t>523837</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>278970</t>
+          <t>280364</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>340519</t>
+          <t>342477</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>748787</t>
+          <t>748294</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>841854</t>
+          <t>841067</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>260775</t>
+          <t>265636</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>324845</t>
+          <t>326423</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>147929</t>
+          <t>148689</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>197988</t>
+          <t>198282</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>423784</t>
+          <t>425035</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>508018</t>
+          <t>505496</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>155441</t>
+          <t>153117</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>208096</t>
+          <t>204241</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>86254</t>
+          <t>84026</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>125916</t>
+          <t>123897</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>251557</t>
+          <t>252728</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>319640</t>
+          <t>316040</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2016</t>
+          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>30459</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55090</t>
+          <t>54374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33257</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56671</t>
+          <t>56471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71012</t>
+          <t>70093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104514</t>
+          <t>102659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30752</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>56576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21689</t>
+          <t>22622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42568</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59224</t>
+          <t>58887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90391</t>
+          <t>89040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78062</t>
+          <t>77668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108137</t>
+          <t>108892</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>41799</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>64594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>125045</t>
+          <t>126873</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164549</t>
+          <t>164511</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40710</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>67425</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23325</t>
+          <t>23657</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>43237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69557</t>
+          <t>69661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101699</t>
+          <t>104194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32272</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>46157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77025</t>
+          <t>77748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44373</t>
+          <t>46422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73241</t>
+          <t>73410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98971</t>
+          <t>100036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140547</t>
+          <t>140725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64324</t>
+          <t>64354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96183</t>
+          <t>95958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>32022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54983</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101617</t>
+          <t>102872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143036</t>
+          <t>144092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130800</t>
+          <t>130966</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>172519</t>
+          <t>170898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85256</t>
+          <t>86627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118788</t>
+          <t>117999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>226329</t>
+          <t>230089</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>277888</t>
+          <t>281468</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66424</t>
+          <t>65788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99988</t>
+          <t>98990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41518</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70108</t>
+          <t>66826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112540</t>
+          <t>112827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155965</t>
+          <t>156832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>30242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56004</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47565</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78257</t>
+          <t>77766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37483</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65359</t>
+          <t>65516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>25373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>47729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68837</t>
+          <t>68681</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105098</t>
+          <t>105024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43741</t>
+          <t>43639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75285</t>
+          <t>74239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>32023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56821</t>
+          <t>55211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83562</t>
+          <t>83438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122045</t>
+          <t>121350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82389</t>
+          <t>82578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>117963</t>
+          <t>116811</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75007</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104117</t>
+          <t>106935</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>167097</t>
+          <t>166493</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>213287</t>
+          <t>213000</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87547</t>
+          <t>89186</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123718</t>
+          <t>124532</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56684</t>
+          <t>55922</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85841</t>
+          <t>84659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>153258</t>
+          <t>151400</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201930</t>
+          <t>200963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65307</t>
+          <t>66833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43876</t>
+          <t>43660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69050</t>
+          <t>66550</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100947</t>
+          <t>101213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65335</t>
+          <t>65415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97264</t>
+          <t>98845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52833</t>
+          <t>51077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84292</t>
+          <t>82770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125148</t>
+          <t>125494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169882</t>
+          <t>167674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60780</t>
+          <t>60570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93465</t>
+          <t>93413</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43976</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73237</t>
+          <t>72559</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116286</t>
+          <t>116177</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>156642</t>
+          <t>156036</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>114504</t>
+          <t>115742</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>153858</t>
+          <t>152436</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85050</t>
+          <t>85477</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119315</t>
+          <t>119911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>210881</t>
+          <t>212468</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263200</t>
+          <t>259660</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53393</t>
+          <t>53677</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85358</t>
+          <t>83488</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49163</t>
+          <t>48763</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77226</t>
+          <t>77484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110321</t>
+          <t>112074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154861</t>
+          <t>153552</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55458</t>
+          <t>55528</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49435</t>
+          <t>50683</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65312</t>
+          <t>62136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99901</t>
+          <t>96883</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>206193</t>
+          <t>204612</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>265621</t>
+          <t>261645</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>178282</t>
+          <t>179950</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>231780</t>
+          <t>233051</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>400911</t>
+          <t>398580</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>479299</t>
+          <t>474151</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>224209</t>
+          <t>227741</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>287348</t>
+          <t>288297</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>150350</t>
+          <t>149475</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>198210</t>
+          <t>197579</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>395108</t>
+          <t>395718</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>473822</t>
+          <t>471149</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>441794</t>
+          <t>441804</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>517757</t>
+          <t>514724</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>313690</t>
+          <t>314964</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>375442</t>
+          <t>375868</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>769590</t>
+          <t>769675</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>862478</t>
+          <t>867374</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>275791</t>
+          <t>277500</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>337816</t>
+          <t>342605</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>192748</t>
+          <t>191918</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>244927</t>
+          <t>246601</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>485039</t>
+          <t>486653</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>570208</t>
+          <t>569171</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>124547</t>
+          <t>126568</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>171696</t>
+          <t>173751</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>79862</t>
+          <t>80549</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>116654</t>
+          <t>118139</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>215494</t>
+          <t>217726</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>276679</t>
+          <t>278290</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2023</t>
+          <t>Población según si la distribución de tareas es irregular y provoca que se le acumule el trabajo en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>33644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56277</t>
+          <t>55239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38226</t>
+          <t>37480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47272</t>
+          <t>47591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34735</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27370</t>
+          <t>25882</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>32822</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55612</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>41863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18026</t>
+          <t>19138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>24648</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68418</t>
+          <t>68019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>358759</t>
+          <t>357090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>29085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87680</t>
+          <t>86854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>437057</t>
+          <t>438699</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>39676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>23127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60992</t>
+          <t>61788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17172</t>
+          <t>19668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189428</t>
+          <t>190160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46366</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34656</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>214436</t>
+          <t>215550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89741</t>
+          <t>90878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33824</t>
+          <t>34824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118912</t>
+          <t>116510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49697</t>
+          <t>50656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29695</t>
+          <t>29757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49703</t>
+          <t>48124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23169</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13892</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33779</t>
+          <t>32942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>36037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38884</t>
+          <t>38639</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46996</t>
+          <t>46113</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70935</t>
+          <t>71049</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41728</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>59366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40370</t>
+          <t>39641</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67268</t>
+          <t>65721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93107</t>
+          <t>93252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24165</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44019</t>
+          <t>44155</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32857</t>
+          <t>33692</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32904</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55832</t>
+          <t>56818</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>40735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>172551</t>
+          <t>172802</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>548362</t>
+          <t>543614</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109764</t>
+          <t>107779</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>268074</t>
+          <t>268280</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>721896</t>
+          <t>762670</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108570</t>
+          <t>109226</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40536</t>
+          <t>41192</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63216</t>
+          <t>62646</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>157798</t>
+          <t>158923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55507</t>
+          <t>55833</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>230868</t>
+          <t>232926</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>98816</t>
+          <t>96402</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>125042</t>
+          <t>126062</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>114318</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>342885</t>
+          <t>338030</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30911</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>135247</t>
+          <t>135126</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>56973</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>84183</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>79347</t>
+          <t>71987</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>205610</t>
+          <t>204416</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>44708</t>
+          <t>48090</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20580</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>23886</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>75705</t>
+          <t>77341</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6702-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6702-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43337</t>
+          <t>43320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69499</t>
+          <t>70402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>21010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42191</t>
+          <t>42987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70633</t>
+          <t>69242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104390</t>
+          <t>102472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64391</t>
+          <t>63991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>28664</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51258</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69250</t>
+          <t>72011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106043</t>
+          <t>107480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71349</t>
+          <t>72793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102732</t>
+          <t>103672</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41631</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64958</t>
+          <t>64972</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121945</t>
+          <t>120337</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161947</t>
+          <t>160206</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46074</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>73608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35372</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67034</t>
+          <t>66678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101032</t>
+          <t>98988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29163</t>
+          <t>29352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>22294</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>44687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60329</t>
+          <t>58196</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94033</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>45536</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>75974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112274</t>
+          <t>114201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156605</t>
+          <t>157479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39856</t>
+          <t>40227</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68118</t>
+          <t>68033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30341</t>
+          <t>30198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55660</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76819</t>
+          <t>78481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114649</t>
+          <t>114492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117225</t>
+          <t>117159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154869</t>
+          <t>155632</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74708</t>
+          <t>75596</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109350</t>
+          <t>109199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>201352</t>
+          <t>198491</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>253244</t>
+          <t>248668</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73966</t>
+          <t>73759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107849</t>
+          <t>105037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37414</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64318</t>
+          <t>63579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,47 +1803,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>139394</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>117812</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>161012</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>23,68%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>139394</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>117888</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>162264</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>20,5%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41508</t>
+          <t>42324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71948</t>
+          <t>73313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t>42715</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69348</t>
+          <t>68438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105905</t>
+          <t>105368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30605</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54880</t>
+          <t>55656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35178</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60909</t>
+          <t>60704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71210</t>
+          <t>70189</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108013</t>
+          <t>107046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35383</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63690</t>
+          <t>64311</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>38884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>58508</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93670</t>
+          <t>93722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84723</t>
+          <t>86306</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120120</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47265</t>
+          <t>47043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75671</t>
+          <t>74563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>139511</t>
+          <t>139776</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>182476</t>
+          <t>185582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50410</t>
+          <t>50734</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81757</t>
+          <t>80862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28379</t>
+          <t>27768</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52694</t>
+          <t>52328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86054</t>
+          <t>86681</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>126412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>51011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82880</t>
+          <t>82793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28088</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52442</t>
+          <t>53715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86771</t>
+          <t>86223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125954</t>
+          <t>125289</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58314</t>
+          <t>59854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93831</t>
+          <t>94187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60241</t>
+          <t>58818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89605</t>
+          <t>90263</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129064</t>
+          <t>127380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>174581</t>
+          <t>173133</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>79248</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31209</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55595</t>
+          <t>55967</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87415</t>
+          <t>89198</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126279</t>
+          <t>127173</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141112</t>
+          <t>141651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180900</t>
+          <t>183927</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>89872</t>
+          <t>88621</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124129</t>
+          <t>122845</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>240241</t>
+          <t>242119</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>294490</t>
+          <t>296741</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,2%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>66210</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95715</t>
+          <t>97194</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45108</t>
+          <t>46088</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74916</t>
+          <t>74496</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117497</t>
+          <t>119099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161970</t>
+          <t>163211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27653</t>
+          <t>28060</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51555</t>
+          <t>52457</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29554</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44528</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>74262</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>215803</t>
+          <t>221141</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>277016</t>
+          <t>278286</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>181933</t>
+          <t>185941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>239420</t>
+          <t>239292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>418870</t>
+          <t>417761</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>501195</t>
+          <t>500646</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>185001</t>
+          <t>184924</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>242752</t>
+          <t>243459</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>127400</t>
+          <t>129838</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>175424</t>
+          <t>176047</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>326799</t>
+          <t>325279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>400888</t>
+          <t>402008</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>453313</t>
+          <t>450519</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>523837</t>
+          <t>524092</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>280364</t>
+          <t>279662</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>342477</t>
+          <t>338623</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>748294</t>
+          <t>749166</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>841067</t>
+          <t>844814</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>265636</t>
+          <t>260722</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>326423</t>
+          <t>322644</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>148689</t>
+          <t>150072</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>198282</t>
+          <t>198857</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>425035</t>
+          <t>425479</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>505496</t>
+          <t>506485</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>153117</t>
+          <t>155447</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>204241</t>
+          <t>206271</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>84286</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>123897</t>
+          <t>125310</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>252728</t>
+          <t>251338</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>316040</t>
+          <t>317305</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30459</t>
+          <t>31179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54374</t>
+          <t>56096</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34116</t>
+          <t>34816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56471</t>
+          <t>57576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70093</t>
+          <t>70637</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102659</t>
+          <t>103946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32125</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56576</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42158</t>
+          <t>41886</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58887</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89040</t>
+          <t>89228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77668</t>
+          <t>77687</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108892</t>
+          <t>107374</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41799</t>
+          <t>41157</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64594</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126873</t>
+          <t>125895</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164511</t>
+          <t>165051</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40839</t>
+          <t>40421</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67425</t>
+          <t>65509</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43237</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69661</t>
+          <t>69653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104194</t>
+          <t>103401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22597</t>
+          <t>22730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32344</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46157</t>
+          <t>47715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77748</t>
+          <t>78697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46422</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73410</t>
+          <t>71295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100036</t>
+          <t>100074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140725</t>
+          <t>140143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64354</t>
+          <t>63515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95958</t>
+          <t>95812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32022</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102872</t>
+          <t>101759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144092</t>
+          <t>142159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130966</t>
+          <t>131010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>170898</t>
+          <t>173302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86627</t>
+          <t>85608</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117999</t>
+          <t>118118</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>230089</t>
+          <t>226158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>281468</t>
+          <t>278420</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65788</t>
+          <t>65329</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98990</t>
+          <t>98557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>67177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112827</t>
+          <t>115528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156832</t>
+          <t>158167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>30738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>55298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47202</t>
+          <t>47087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77766</t>
+          <t>78755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37145</t>
+          <t>37296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65516</t>
+          <t>65941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68681</t>
+          <t>68827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105024</t>
+          <t>104775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43639</t>
+          <t>44037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74239</t>
+          <t>74333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>54686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83438</t>
+          <t>83742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121350</t>
+          <t>123646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>81741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116811</t>
+          <t>117524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76714</t>
+          <t>75133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106935</t>
+          <t>105994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>166493</t>
+          <t>166822</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>213000</t>
+          <t>211604</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89186</t>
+          <t>88562</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124532</t>
+          <t>125132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55922</t>
+          <t>56477</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84659</t>
+          <t>86007</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>151400</t>
+          <t>154086</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200963</t>
+          <t>201284</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66833</t>
+          <t>66401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>44446</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>66626</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101213</t>
+          <t>102422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65415</t>
+          <t>64512</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98845</t>
+          <t>97527</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51077</t>
+          <t>51734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82770</t>
+          <t>83155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125494</t>
+          <t>126457</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167674</t>
+          <t>168627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>60570</t>
+          <t>61866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93413</t>
+          <t>93264</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43168</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>72559</t>
+          <t>73219</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116177</t>
+          <t>115130</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>156036</t>
+          <t>156934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>115742</t>
+          <t>115259</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>152436</t>
+          <t>154157</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>85477</t>
+          <t>85535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119911</t>
+          <t>118683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>212468</t>
+          <t>207839</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>259660</t>
+          <t>258480</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53677</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>83488</t>
+          <t>85044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>48765</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>77484</t>
+          <t>78673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112074</t>
+          <t>111652</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153552</t>
+          <t>155135</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55528</t>
+          <t>55430</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50683</t>
+          <t>49809</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62136</t>
+          <t>62104</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96883</t>
+          <t>97928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>204612</t>
+          <t>204620</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>261645</t>
+          <t>262435</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>179950</t>
+          <t>180684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>233051</t>
+          <t>230823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>398580</t>
+          <t>401303</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>474151</t>
+          <t>478183</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>227741</t>
+          <t>227575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>288297</t>
+          <t>285517</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>149475</t>
+          <t>151911</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>197579</t>
+          <t>199485</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,47 +7265,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>430321</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>391265</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>468476</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>19,05%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>430321</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>395718</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>471149</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>16,09%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>441804</t>
+          <t>439575</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>514724</t>
+          <t>513727</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>314964</t>
+          <t>315812</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>375868</t>
+          <t>373674</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>769675</t>
+          <t>768399</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>867374</t>
+          <t>869341</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>277500</t>
+          <t>275900</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>342605</t>
+          <t>341631</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>191918</t>
+          <t>191389</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>246601</t>
+          <t>245255</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>486653</t>
+          <t>486375</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>569171</t>
+          <t>569914</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>126568</t>
+          <t>125062</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>173751</t>
+          <t>172379</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>80549</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>118139</t>
+          <t>116292</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>217726</t>
+          <t>216491</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>278290</t>
+          <t>275528</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>24185</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33644</t>
+          <t>36629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27664</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>46627</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>33856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>62341</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,32 +8194,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>33463</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47591</t>
+          <t>48630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>26541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>15580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,22 +8307,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>43267</t>
+          <t>48605</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32822</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>61625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30918</t>
+          <t>34006</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>23708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41863</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19138</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>13245</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24648</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>274219</t>
+          <t>35103</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68019</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>357090</t>
+          <t>48142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13407</t>
+          <t>16859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>294637</t>
+          <t>58815</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86854</t>
+          <t>44807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>438699</t>
+          <t>73581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39676</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>29006</t>
+          <t>30470</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61788</t>
+          <t>41832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68748</t>
+          <t>73777</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>58627</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>190160</t>
+          <t>88583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>42294</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29816</t>
+          <t>33474</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46649</t>
+          <t>52921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>106873</t>
+          <t>116072</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>100428</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>215550</t>
+          <t>135054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31059</t>
+          <t>37288</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>26624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90878</t>
+          <t>50634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34824</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>57130</t>
+          <t>66391</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116510</t>
+          <t>82093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>23967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21001</t>
+          <t>22021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50656</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>114560</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>114560</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>114560</t>
+          <t>126522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>511130</t>
+          <t>298421</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>511130</t>
+          <t>298421</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>511130</t>
+          <t>298421</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>41500</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48124</t>
+          <t>54218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26569</t>
+          <t>35741</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>25099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36037</t>
+          <t>48640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>34007</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>26179</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38639</t>
+          <t>42249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>57401</t>
+          <t>69748</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>55363</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71049</t>
+          <t>86187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>19389</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>37762</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47918</t>
+          <t>53701</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38237</t>
+          <t>41815</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59366</t>
+          <t>65388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31951</t>
+          <t>35197</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23890</t>
+          <t>26426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39641</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>79869</t>
+          <t>88899</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65721</t>
+          <t>74039</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93252</t>
+          <t>101484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13889</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18820</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>32709</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24510</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44155</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>32403</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>23826</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>31739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>44227</t>
+          <t>46344</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34232</t>
+          <t>36061</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>58482</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28637</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>30545</t>
+          <t>32473</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>23157</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11117</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>20146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>360810</t>
+          <t>131141</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>172802</t>
+          <t>109991</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>543614</t>
+          <t>153720</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>93867</t>
+          <t>104699</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>79959</t>
+          <t>89759</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>107779</t>
+          <t>122192</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>454678</t>
+          <t>235841</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>268280</t>
+          <t>209566</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>762670</t>
+          <t>261054</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>52513</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>109226</t>
+          <t>89813</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>50695</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62646</t>
+          <t>67784</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>113585</t>
+          <t>124005</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48614</t>
+          <t>102696</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>158923</t>
+          <t>147672</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>140793</t>
+          <t>158577</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55833</t>
+          <t>135974</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>232926</t>
+          <t>183306</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>110975</t>
+          <t>122192</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>96402</t>
+          <t>105494</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>126062</t>
+          <t>138158</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>251768</t>
+          <t>280769</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114318</t>
+          <t>252296</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>338030</t>
+          <t>313661</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>81179</t>
+          <t>92361</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31267</t>
+          <t>73745</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>135126</t>
+          <t>111587</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>68568</t>
+          <t>78270</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>55370</t>
+          <t>65228</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>82827</t>
+          <t>92298</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>149747</t>
+          <t>170631</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71987</t>
+          <t>148646</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>204416</t>
+          <t>196034</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>48090</t>
+          <t>47111</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>33120</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39002</t>
+          <t>45047</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>53455</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>23886</t>
+          <t>47529</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77341</t>
+          <t>83907</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>353110</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>353110</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>353110</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1023233</t>
+          <t>873666</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1023233</t>
+          <t>873666</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1023233</t>
+          <t>873666</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
